--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1910,6 +1910,7530 @@
         <v>1.79</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:23</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>8f85a9b2ecab41b6a8171feb05a2c7cf.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:39</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>29241c82b6da46268177aa1d3f9a8bd8.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:44</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>e0a351a8ec5a41d7816b0852c82fa34c.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>56.66</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Gonyosoma oxycephalum</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:50</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>3d5eefd1de794106a1f915d20c66e8aa.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:53</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1c636bf2298e4789908910d61d3680c5.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Gonyosoma oxycephalum</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:55:57</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>8269313b886a48a6a329e2cc51ff224a.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bothriechis schlegelii</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:56:02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4dd3733efd9f4ca48c901fceaac05ad1.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Boiga kraepelini</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:56:06</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>da4f8c88523347bca03e20a63653050d.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>94.33</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Thamnophis radix</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:56:11</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fc08a45badfe4e66ae6c2ee373697f7e.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>48.63</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Ninia sebae</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>8.01</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025-10-22 20:56:16</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>4dd3733efd9f4ca48c901fceaac05ad1.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Boiga kraepelini</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025-10-22 21:08:46</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>3ecead6982114001a3596c048efbe1d8.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Opheodrys aestivus</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>18.83</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Dendrelaphis pictus</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025-10-22 21:09:12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>b890e1192f64402eaaeffb064da6928d.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ninia sebae</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:41:31</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:44:41</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>94462f5278c9474eb3cdd77a28ca0766.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>47.22</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Bitis arietans</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Daboia russelii</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:47:59</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:48:02</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:49:01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025-10-24 14:50:09</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2025-10-24 15:05:51</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025-10-24 15:59:32</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025-10-24 15:59:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>47e66615150d428c87fae079c80c2d97.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>87.18000000000001</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Micrurus fulvius</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Imantodes cenchoa</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:02:06</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:02:53</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:03:47</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>66117ee4956b4711a81df19a193ef016.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Morelia spilota</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>9.109999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:03:50</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:05:07</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:07:42</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:10:28</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:13:49</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:13:54</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>019776b5ff4f418099f3ed8f6dd45a2f.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Micrurus fulvius</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>82.81999999999999</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:14:00</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>e6eeb3e28311450795854a5c0e4a4a4b.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Micrurus fulvius</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Epicrates cenchria</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:14:08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>47e66615150d428c87fae079c80c2d97.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>87.18000000000001</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Micrurus fulvius</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Imantodes cenchoa</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:19:56</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:20:22</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:21:43</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:23:30</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:24:45</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>e6eeb3e28311450795854a5c0e4a4a4b.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Micrurus fulvius</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Epicrates cenchria</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>21.37</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:24:50</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>a18d36993fe442a5a58d0fe09f9a83db.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Micrurus tener</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>99.97</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:25:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>a1fce94488e2417ab560df21fbf21041.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lampropeltis getula</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:27:26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2c9c05c202824e5da35e30b202602cc9.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>89</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ahaetulla prasina</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Opheodrys aestivus</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:27:35</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ef59c193e1b44510886d8f07326576eb.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:27:57</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2238f07a80224c58bf7d9aaae4e36cc1.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Thamnophis radix</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Masticophis lateralis</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Thamnophis marcianus</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>11.55</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:28:05</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ef59c193e1b44510886d8f07326576eb.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:28:34</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>86ea4ef7b30f406ca1cc2aee8b2662e5.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tropidolaemus subannulatus</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025-10-24 16:29:10</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ca51c395b02f4b15b8749f4e0adeb794.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Tropidolaemus subannulatus</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>80.22</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Bothriechis schlegelii</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:01:08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>86ea4ef7b30f406ca1cc2aee8b2662e5.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tropidolaemus subannulatus</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:32</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>b63cdbb4e4d845f197899abaa7fc9241.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>19.19</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:35</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ce9b45d14fb04148a3df1e9f6e6922d0.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Tantilla planiceps</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:40</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>e7636a1581d6479eb95ae3105451b3af.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>53.05</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>12.81</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:46</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>dc7fe272eccf49f4b960c5113477d683.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Tropidoclonion lineatum</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Salvadora hexalepis</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>23.14</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:51</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>80fe1d7be56b4125a1ece1c505249b10.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Masticophis bilineatus</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>39.21</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>35.53</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:02:54</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>dc7fe272eccf49f4b960c5113477d683.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Tropidoclonion lineatum</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Salvadora hexalepis</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>23.14</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:00</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>a183204f2b984b688be9d6731dccc219.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Thamnophis proximus</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Thamnophis radix</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Salvadora grahamiae</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:04</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>e52dc0051541457fa433e42abfd7eb85.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Thamnophis proximus</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Thamnophis cyrtopsis</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>8.279999999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>fe32129f9d3e4129b7fe92db2068d8da.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Crotalus tigris</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:13</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>66b802035c6c4a43b8d956ab629df614.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Epicrates cenchria</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>52.73</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>40.63</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>1.95</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:15</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>d29ce4a4453a436e8bcde4c9c5284a03.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>83.11</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Bungarus multicinctus</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:22</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2e557eb184e549cbb43758cb0f8303ef.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>99.02</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:27</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>804e486dee5f414b9778a0d82c3f654c.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:32</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>58ae9c716b0e41d29c100c2d1ba49a55.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Drymarchon couperi</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>2.24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:40</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>8da5d39041214f7b9d3a44dde6a0b4e1.jpg</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>86.95</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Crotalus lepidus</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>2.26</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:43</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>e372d3a2c7674125b91d42dc6772bab6.jpg</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Crotalus lepidus</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>6.61</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:47</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1c23e5d55f8c452ab68c31f9003a2b72.jpg</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Bitis gabonica</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:50</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>f0d4bc938cc64a73a52b094fd8f3f550.jpg</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Crotalus viridis</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>16.32</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:03:55</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>40b8a10ef4bc4a5998a4c1c2f9b8a359.jpg</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Python regius</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:00</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>e1cf9db2f43d40ac81c82e8b6a9293da.jpg</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>95.52</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Boiga kraepelini</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>1.14</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:04</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>ddf4ba88d72f4a54951524542ba03477.jpg</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>85.68000000000001</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Crotalus ruber</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Bothrops atrox</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>40b8a10ef4bc4a5998a4c1c2f9b8a359.jpg</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>92.51000000000001</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Python regius</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:13</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1766837da921423eaee0f5cd1897f325.jpg</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Pseudonaja textilis</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:16</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>36a870fa34734abab1d2f25e07e4905d.jpg</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>92.37</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Vipera seoanei</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Nerodia cyclopion</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>d1f59230182045a1b2a0edad71fa6525.jpg</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Vipera seoanei</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Diadophis punctatus</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:04:23</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>d24dd7dd40444d3dab2b26cfddb13865.jpg</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:07:20</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>403bf8e76a6a43f0907deb08fae2be19.jpg</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>32</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:07:29</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>403bf8e76a6a43f0907deb08fae2be19.jpg</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>32</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:10:58</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>be1120a0f8374abb920c56120469565c.jpg</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>70.79000000000001</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Nerodia floridana</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Atractus crassicaudatus</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>3.02</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:11:17</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1766837da921423eaee0f5cd1897f325.jpg</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pseudonaja textilis</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:11:29</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>a3ccd28e4fa44fc7ad499845e5d646b2.jpg</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>10.42</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:11:34</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>d24dd7dd40444d3dab2b26cfddb13865.jpg</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:11</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>6da1c9c6f8884305b23e9dbc1e04b04c.jpg</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Coronella girondica</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Heterodon simus</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>21.83</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>d48c72a244cd458c9d4f641ff8214404.jpg</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Dendrelaphis punctulatus</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Gonyosoma oxycephalum</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Rhabdophis subminiatus</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:27</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>584d61866b034287819a68ed4b4dc92d.jpg</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Dendrelaphis punctulatus</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>99.67</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Opheodrys aestivus</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Gonyosoma oxycephalum</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:31</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>eee2b48234534b0e9d1d5c473f6e0bec.jpg</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Spilotes pullatus</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>53.01</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Thamnophis couchii</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:34</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>58ea233951c7487eba50fe49231c7142.jpg</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Dendrelaphis punctulatus</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>87.64</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Rhabdophis subminiatus</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Leptophis mexicanus</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:38</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>fd787866bf3043088a254d6ae66f4f5c.jpg</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Dendrelaphis punctulatus</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Hierophis viridiflavus</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Thamnophis couchii</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:42</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>147c23947d6742509f7dee81e7499c9c.jpg</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dendrelaphis punctulatus</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>68.56999999999999</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Dendroaspis polylepis</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>8.31</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:12:51</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>b64055eaacce4daa9d399341a210047f.jpg</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Masticophis taeniatus</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Carphophis vermis</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:13:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>b5722f378ca242f79b2146c95fcc5f70.jpg</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>21.83</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>19.33</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:13:11</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>f6c549458f4d4cbd8d12496eeb389264.jpg</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:02</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5d0d0011270649b9a81948e79ca898f9.jpg</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Bothrops atrox</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>7c276072e7dc44e9887e4e54d055d85f.jpg</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Senticolis triaspis</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Rhabdophis subminiatus</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:16</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>f13083a3b1e54007aeb0c20f6d034d65.jpg</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>70.14</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>18.64</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Eunectes murinus</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>7.04</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:20</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>d0393e2983f94d439d7d4c17e74b5eb1.jpg</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>67.52</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Rhabdophis subminiatus</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Boiga irregularis</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:24</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>91ee541729b04cc69fde50fa473a3aef.jpg</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Rhabdophis subminiatus</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:28</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>270849fb57df4243a425bd19888fc31a.jpg</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>79.84999999999999</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Lycodon capucinus</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>3.54</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:37</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>f82707aabd5b4de69f2a479035b75020.jpg</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:41</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>f4f105b7220a44109b0272e9d3415e63.jpg</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aspidites melanocephalus</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Bungarus multicinctus</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:33:51</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>49d8b8d531cd4f34ba28193de9079c4a.jpg</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>54.01</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>12.48</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:34:09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>0884d3906973426abfe83c0178add9d0.jpg</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Python regius</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Epicrates cenchria</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Bogertophis subocularis</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:34:45</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>8b1a47e1d7eb478eb23237679a5016b7.jpg</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lampropeltis zonata</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:34:50</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>aae1c926b5d84fa4b9e579985f00ffb1.jpg</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Senticolis triaspis</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:34:57</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>b82edfdec4bf4d58ba2f26b07a913deb.jpg</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Bungarus multicinctus</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Laticauda colubrina</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:19</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>0084470ba0b44e1e8bfed8b84aea1cab.jpg</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Tropidoclonion lineatum</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:23</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>4705b8c75d6245328476bfc4317936b0.jpg</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Thamnophis couchii</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Salvadora hexalepis</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>5.98</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>275e6de3ca3b4caa99b1366c1161ec84.jpg</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>69.13</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:30</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>df69444abec24c65b5f66568e55f34bd.jpg</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Agkistrodon contortrix</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Bungarus multicinctus</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:35</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>0d4aaf743fa142f98bb0ec62a75e10fc.jpg</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Thamnophis cyrtopsis</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Thamnophis couchii</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:38</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3b263ecb548b4b6cab098a34d9ac5ffc.jpg</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>87.23999999999999</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:49</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>04079e76c6e84fec9cc131f058314d8f.jpg</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Lampropeltis getula</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Drymarchon couperi</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:35:53</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>fb0162f0d55f4649ac31543874e55b55.jpg</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Lampropeltis getula</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>94.94</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Ophiophagus hannah</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Vipera seoanei</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:08</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>43152026e2264536a5a524f47fe5d3df.jpg</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>12.79</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2c2536cc3bcd4685b5e1185dd279b533.jpg</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>46.28</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:16</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ab6c5657e3fe481790962795c1ec5a37.jpg</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Carphophis vermis</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>18.18</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:20</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>d00426a39d3e436bafdd21a01fa87714.jpg</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Regina septemvittata</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:26</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1766837da921423eaee0f5cd1897f325.jpg</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Pseudonaja textilis</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:30</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>403bf8e76a6a43f0907deb08fae2be19.jpg</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>32</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:33</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>d1f59230182045a1b2a0edad71fa6525.jpg</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>60.85</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Vipera seoanei</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>14.06</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Diadophis punctatus</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:36</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>d24dd7dd40444d3dab2b26cfddb13865.jpg</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>93.06</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:36:42</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>7c683ba39e124ba8b7778576a84863f7.jpg</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:37:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1766837da921423eaee0f5cd1897f325.jpg</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Pseudechis porphyriacus</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Pseudonaja textilis</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:37:26</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>f82707aabd5b4de69f2a479035b75020.jpg</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:37:30</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>a1cc5a22fd7d433fbfed0d30b4c91b7b.jpg</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>68.81</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Crotalus tigris</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>28.62</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:37:35</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>8d5cc9bcd092483581156a917a0998a9.jpg</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Psammodynastes pulverulentus</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Naja naja</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:38:03</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>79250ee297f14c2fbb23a7065b196325.jpg</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Imantodes cenchoa</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>99.86</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Boiga kraepelini</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Corallus hortulanus</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:38:34</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ccdbfc1954d943c4aaabdfdb00b238f1.jpg</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Eunectes murinus</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>96.06999999999999</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Aspidites melanocephalus</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Python molurus</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:38:43</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>866e16071fe64a6d89a4f2db25ac335b.jpg</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ahaetulla prasina</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>95.19</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Imantodes cenchoa</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:38:51</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>f6c54289fc484ae78958831221b37db2.jpg</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Ahaetulla prasina</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Corallus hortulanus</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Psammodynastes pulverulentus</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:39:02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>6dede572097d4c63b221244adbda8a26.jpg</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>98.06</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:39:08</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>159b9f64f26547c2b12cf75d743aa3c6.jpg</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Leptodeira annulata</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>8.67</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:39:14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>df60abc037764894a2fd9f08312cf8b1.jpg</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Crotalus ruber</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:39:22</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>a38f48e6e43b4c589226d84226bce057.jpg</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Heterodon nasicus</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Crotalus ruber</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:15</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>df60abc037764894a2fd9f08312cf8b1.jpg</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>12.93</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Crotalus ruber</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:17</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>f8f075cdf9564386bd5ca75ac84d4cbc.jpg</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>39.16</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>18.12</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:21</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>8c8ddd61341f4fa7b41b94896202a564.jpg</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Crotalus ornatus</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:30</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>8c8ddd61341f4fa7b41b94896202a564.jpg</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Crotalus ornatus</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>41.77</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>12.46</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:44</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>WhatsApp Görsel 2025-10-21 saat 01.18.41_88f7bc1a.jpg</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Python regius</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Aspidites melanocephalus</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Lampropeltis pyromelana</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:40:50</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>WhatsApp Görsel 2025-10-21 saat 01.18.41_88f7bc1a.jpg</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Python regius</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>95.81999999999999</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Aspidites melanocephalus</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Lampropeltis pyromelana</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:23</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>22754d0ee72748ce874eb2e48c1b46e5.jpg</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>28.22</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Crotalus viridis</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:31</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>4239b9fc60914e039ce93c3f754f4fae.jpg</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Crotalus molossus</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>97.95</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Heterodon nasicus</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:35</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>cc79f1bb3bd248ca90769521414456d9.jpg</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Crotalus molossus</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>97.69</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:47</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>8b771013d6d24d9ba72acef978c763b6.jpg</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>72.62</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Arizona elegans</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Senticolis triaspis</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:51</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>f09336247f01436882982842f1a0855e.jpg</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Morelia spilota</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>15.77</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:55</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>f701827929bb468389abed7d6891fd24.jpg</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>69.48</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Senticolis triaspis</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:41:59</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2e9d704ec7364520bc8c5da0b4acea35.jpg</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>55.79</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Crotaphopeltis hotamboeia</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>9.94</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:07</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>b7be90bac5c241b7af9834e2dd946f8f.jpg</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Masticophis taeniatus</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Masticophis bilineatus</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:10</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>f3c65ddf3008447fa814465f655ac872.jpg</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>86.65000000000001</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Masticophis bilineatus</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>8.48</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Masticophis taeniatus</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:13</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>b64055eaacce4daa9d399341a210047f.jpg</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Masticophis taeniatus</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Carphophis vermis</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1faa56d0f0594ee1bdd04b3cc18cf359.jpg</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>31.64</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Nerodia cyclopion</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:22</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>9c69dea02f6d4b18a199932d007ff470.jpg</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Masticophis schotti</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>66.62</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>3.32</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:38</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>b27fbac2ba5346248c5b62c5a416360c.jpg</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Salvadora grahamiae</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>81.06999999999999</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Masticophis taeniatus</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Salvadora hexalepis</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:42:54</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>f58760098dfb4dc398e1b0072bd8c0b2.jpg</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Tantilla planiceps</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>11.02</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:00</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>8f85a9b2ecab41b6a8171feb05a2c7cf.jpg</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:12</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>b15142c99f73426788a97fedbe1e47bb.jpg</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>99.13</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Tropidolaemus subannulatus</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:16</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>ef59c193e1b44510886d8f07326576eb.jpg</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Trimeresurus stejnegeri</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>74.17</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>5.97</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:28</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>57f9edcb99694d24b9405e4f3319228f.jpg</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Tropidolaemus wagleri</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>90.37</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Morelia spilota</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Spilotes pullatus</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:34</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>4f7c104deeff47948fe86f8cccd34179.jpg</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Sistrurus miliarius</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Heterodon simus</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:49</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>0affb26a7671465194be3809e1e2db22.jpg</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Sistrurus miliarius</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Crotalus triseriatus</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:43:59</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>09f0e5d52a8a4a72ab83c0684b7610f8.jpg</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Thamnophis couchii</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Thamnophis atratus</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>2.68</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:44:06</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>848cbd1178f746839fdada6d3cf3d29b.jpg</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Phyllorhynchus decurtatus</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Hypsiglena torquata</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Crotalus stephensi</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025-10-24 17:44:09</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>d50b2c9947664a2d9768c2504d998a7c.jpg</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Phyllorhynchus decurtatus</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>88.64</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Crotalus cerastes</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025-10-25 17:01:44</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>752207aa832d4108add8731b7eea7eb4.jpg</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Phyllorhynchus decurtatus</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>96.02</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Crotalus ornatus</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Crotalus atrox</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:02:00</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>8f85a9b2ecab41b6a8171feb05a2c7cf.jpg</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>72.34</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:03:34</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>a183204f2b984b688be9d6731dccc219.jpg</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Thamnophis proximus</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Thamnophis radix</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>42.09</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Salvadora grahamiae</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:04:41</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>77a17b2ea2ee4573aef867a04ba112da.jpg</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Leptophis diplotropis</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Leptophis ahaetulla</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>18.52</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Leptophis mexicanus</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:05:02</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>d6982c4bc48647639a4042ef492f5198.jpg</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>99.83</v>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Morelia viridis</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Gonyosoma oxycephalum</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:05:21</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>9b772b20a8184247908272ef2b0a95e9.jpg</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Dendrelaphis pictus</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Ophiophagus hannah</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Lampropeltis pyromelana</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:05:37</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>c467634fa74e4d1e84713850e7178716.jpg</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Atractus crassicaudatus</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>29.24</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>6.33</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:05:46</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>89984089b83a46ea95f919b66a4f0108.jpg</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Crotalus triseriatus</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Sistrurus miliarius</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Causus rhombeatus</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:01</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>3de7ad1ddf2d44568fd4e890c557ca59.jpg</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Lampropeltis zonata</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Lampropeltis pyromelana</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Cemophora coccinea</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:08</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>7acce4806fd4446a9455e1ce9fe71b35.jpg</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Corallus hortulanus</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Morelia spilota</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:12</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>8d5cc9bcd092483581156a917a0998a9.jpg</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Psammodynastes pulverulentus</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>90.56</v>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Naja naja</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:17</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>047916790060488f81c0d560cdbddb8a.jpg</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Psammodynastes pulverulentus</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>97.87</v>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Bothrops asper</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:24</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>a78d5cfa20a04b8ba8554e5909bb41bf.jpg</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:29</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ac7aed41fa624c2cbe1be06c932ebc81.jpg</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:06:34</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>6ffa0c1a6b9f4c95947d19163a037f31.jpg</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>25.49</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>12.03</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:36</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>623bc891e6ad4d9b8aced4a95f74be4f.jpg</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Naja naja</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>96.06999999999999</v>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Corallus caninus</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Malpolon monspessulanus</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:43</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>a78d5cfa20a04b8ba8554e5909bb41bf.jpg</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Tantilla hobartsmithi</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>16.84</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:46</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>b2c448bc7da04e648c67333b0e5b2d15.jpg</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Tantilla planiceps</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:49</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ac7aed41fa624c2cbe1be06c932ebc81.jpg</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D219" t="n">
+        <v>74.33</v>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>7.82</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:54</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>0fffd930f6574c42bc0522bc2ffcc53d.jpg</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:13:58</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>cbc13baed88949f982aef7f7e16371f0.jpg</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Virginia valeriae</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Contia tenuis</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:01</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>e57bc553ba664760a9cf1f0d9db61b43.jpg</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Carphophis amoenus</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:05</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>d33e325ada5e4ef6907434c444f4d637.jpg</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Rhadinaea flavilata</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>63.23</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Tantilla gracilis</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Tantilla coronata</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:10</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>363a1b56de3e461caa93fae9a38603bc.jpg</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:15</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>868c7973a7a946f7bc58bd18eb84286e.jpg</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Nerodia cyclopion</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:18</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>fd0d93e2c4e444fe93023a0f1f7cb816.jpg</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Vipera ammodytes</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Psammodynastes pulverulentus</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:22</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>efefe82fff764db2a3a8ce3ce8c5027a.jpg</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Sistrurus catenatus</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>5.31</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:25</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>cd55f34695fb4ed892f37fe682967f25.jpg</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Clonophis kirtlandii</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:29</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2727e548a7c947a8af90b37ab9cea5f7.jpg</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>90.78</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:33</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>363a1b56de3e461caa93fae9a38603bc.jpg</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:38</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>868c7973a7a946f7bc58bd18eb84286e.jpg</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Nerodia taxispilota</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>96.89</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Nerodia cyclopion</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:43</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>9f0a65c5e8a647f3aceacc275bb94a23.jpg</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Naja nivea</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Lampropeltis getula</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>4.16</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:47</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>8af3541c83754b589a0147b66dcec059.jpg</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>50.85</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Pseudonaja textilis</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:50</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>eb8b53d67d884d0988ee6f74c114259f.jpg</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Xenochrophis piscator</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Leptodeira annulata</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Heterodon nasicus</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>6.84</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:53</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>cde1e52cfc324bb2902809e1e1d1bebd.jpg</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:14:56</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>d9b48ade02c44ed69989129ce23cae23.jpg</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Pseudaspis cana</t>
+        </is>
+      </c>
+      <c r="D236" t="n">
+        <v>21.73</v>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Sistrurus catenatus</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Crotalus triseriatus</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>8.789999999999999</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:15:02</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>8b1a47e1d7eb478eb23237679a5016b7.jpg</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="D237" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Lampropeltis triangulum</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Lampropeltis zonata</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:15:05</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>aae1c926b5d84fa4b9e579985f00ffb1.jpg</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Pituophis deppei</t>
+        </is>
+      </c>
+      <c r="D238" t="n">
+        <v>80.81999999999999</v>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Senticolis triaspis</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025-10-26 23:15:10</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>b5dcfff696f6434e9866c9b9d2930ebc.jpg</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Rhinocheilus lecontei</t>
+        </is>
+      </c>
+      <c r="D239" t="n">
+        <v>78.38</v>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Farancia abacura</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Lampropeltis alterna</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025-11-03 17:11:00</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>02b4b6ded750486391a8362e6344d000.jpg</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Agkistrodon piscivorus</t>
+        </is>
+      </c>
+      <c r="D240" t="n">
+        <v>53.68</v>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Bothrops atrox</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Bothrops asper</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>11.27</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2025-11-03 17:11:24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>403bf8e76a6a43f0907deb08fae2be19.jpg</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Austrelaps superbus</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pseudechis australis</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>32</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Oxyuranus scutellatus</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025-11-03 17:11:35</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>f9a4dd529bf6424d89a0c09959154ced.jpg</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Crotalus molossus</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025-11-08 01:17:52</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>f9a4dd529bf6424d89a0c09959154ced.jpg</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Crotalus molossus</t>
+        </is>
+      </c>
+      <c r="F243" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025-11-08 01:19:05</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1c3c63330ab64e0c818fdf517b25dc04.jpg</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>82.69</v>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Crotalus scutulatus</t>
+        </is>
+      </c>
+      <c r="F244" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Heterodon nasicus</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:37:27</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>f9a4dd529bf6424d89a0c09959154ced.jpg</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Crotalus molossus</t>
+        </is>
+      </c>
+      <c r="F245" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:37:34</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>dfcc5380dcff46ba9ea8aacfed3604fb.jpg</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Crotalus adamanteus</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Hemorrhois hippocrepis</t>
+        </is>
+      </c>
+      <c r="F246" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Heterodon simus</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:37:50</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ad6f0482f6b148a5b58420a85f9bbd59.jpg</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>88.54000000000001</v>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Natrix maura</t>
+        </is>
+      </c>
+      <c r="F247" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Thamnophis ordinoides</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:37:55</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>d4e71922ebf3474984dec54e562aaa9d.jpg</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="D248" t="n">
+        <v>52.97</v>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Clonophis kirtlandii</t>
+        </is>
+      </c>
+      <c r="F248" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Lampropeltis calligaster</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>5.57</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:37:58</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>122dec1f07d6486eacfa91d839461856.jpg</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="D249" t="n">
+        <v>61.52</v>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Vipera seoanei</t>
+        </is>
+      </c>
+      <c r="F249" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Vipera aspis</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>6.78</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2025-11-22 14:38:01</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>5daa3ca725404747b8b03e73d341ec22.jpg</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Elaphe dione</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Morelia spilota</t>
+        </is>
+      </c>
+      <c r="F250" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Daboia russelii</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
